--- a/site/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/headings.xlsx
+++ b/site/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -661,7 +661,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Correlation field</t>
+          <t>Integration features</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -671,41 +671,41 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01KAJYVBFRP6R3JB9PAN2GSTET</t>
+          <t>h_01M2J4RR924HFQP87J8HN26C70</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/#h_01KAJYVBFRP6R3JB9PAN2GSTET</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/#h_01M2J4RR924HFQP87J8HN26C70</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Log settings</t>
+          <t>Correlation field</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KADF7R30RFKMHY0T79EWCRN3</t>
+          <t>h_01KAJYVBFRP6R3JB9PAN2GSTET</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/#h_01KADF7R30RFKMHY0T79EWCRN3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/#h_01KAJYVBFRP6R3JB9PAN2GSTET</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Notification center</t>
+          <t>Log settings</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -715,63 +715,63 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01M27Y0T0BEVB4ANDNF0WJYB6W</t>
+          <t>h_01KADF7R30RFKMHY0T79EWCRN3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/#h_01M27Y0T0BEVB4ANDNF0WJYB6W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/#h_01KADF7R30RFKMHY0T79EWCRN3</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Notification Setting</t>
+          <t>Notification center</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KDPQB3FVVKSAF8PTPF0PGM6D</t>
+          <t>h_01M27Y0T0BEVB4ANDNF0WJYB6W</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/#h_01KDPQB3FVVKSAF8PTPF0PGM6D</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/#h_01M27Y0T0BEVB4ANDNF0WJYB6W</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>User creation notifications</t>
+          <t>Notification Setting</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H5</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KHQP25XFSJ9FCJM3FAG2GGR1</t>
+          <t>h_01KDPQB3FVVKSAF8PTPF0PGM6D</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/#h_01KHQP25XFSJ9FCJM3FAG2GGR1</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/#h_01KDPQB3FVVKSAF8PTPF0PGM6D</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>User update notifications</t>
+          <t>User creation notifications</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -781,19 +781,19 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KHQP2D967DX3PZS9JJV4K64E</t>
+          <t>h_01KHQP25XFSJ9FCJM3FAG2GGR1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/#h_01KHQP2D967DX3PZS9JJV4K64E</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/#h_01KHQP25XFSJ9FCJM3FAG2GGR1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>User termination notifications</t>
+          <t>User update notifications</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KHQP2J4EY0VYJVWZFTPDV6B8</t>
+          <t>h_01KHQP2D967DX3PZS9JJV4K64E</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/#h_01KHQP2J4EY0VYJVWZFTPDV6B8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/#h_01KHQP2D967DX3PZS9JJV4K64E</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Success email notification settings</t>
+          <t>User termination notifications</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,19 +825,19 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KHQP2PNAJ40RBN5N00H7W881</t>
+          <t>h_01KHQP2J4EY0VYJVWZFTPDV6B8</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/#h_01KHQP2PNAJ40RBN5N00H7W881</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/#h_01KHQP2J4EY0VYJVWZFTPDV6B8</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Error email notification settings</t>
+          <t>Success email notification settings</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -847,41 +847,41 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KHQP2VF8ZGE96CKEJCXK3ZCF</t>
+          <t>h_01KHQP2PNAJ40RBN5N00H7W881</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/#h_01KHQP2VF8ZGE96CKEJCXK3ZCF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/#h_01KHQP2PNAJ40RBN5N00H7W881</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Log insights</t>
+          <t>Error email notification settings</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KDP15YN0777ANCJA7WNRTTG2</t>
+          <t>h_01KHQP2VF8ZGE96CKEJCXK3ZCF</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/#h_01KDP15YN0777ANCJA7WNRTTG2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/#h_01KHQP2VF8ZGE96CKEJCXK3ZCF</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Report settings</t>
+          <t>Log insights</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -891,19 +891,19 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KAE27T5K7KM9THEYH8DMJ24D</t>
+          <t>h_01KDP15YN0777ANCJA7WNRTTG2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/#h_01KAE27T5K7KM9THEYH8DMJ24D</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/#h_01KDP15YN0777ANCJA7WNRTTG2</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Manage Policy</t>
+          <t>Report settings</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -913,107 +913,107 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KGSEBP9WXRXPTF8MXC4D1YZF</t>
+          <t>h_01KAE27T5K7KM9THEYH8DMJ24D</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/#h_01KGSEBP9WXRXPTF8MXC4D1YZF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/#h_01KAE27T5K7KM9THEYH8DMJ24D</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Password Policy Settings</t>
+          <t>Manage Policy</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KADEHFQ33TNFFYZ7YTR25HQH</t>
+          <t>h_01KGSEBP9WXRXPTF8MXC4D1YZF</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/#h_01KADEHFQ33TNFFYZ7YTR25HQH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/#h_01KGSEBP9WXRXPTF8MXC4D1YZF</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Custom Password Policy</t>
+          <t>Password Policy Settings</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H5</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KHQP1PV9JMN083DBZQP2BAAM</t>
+          <t>h_01KADEHFQ33TNFFYZ7YTR25HQH</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/#h_01KHQP1PV9JMN083DBZQP2BAAM</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/#h_01KADEHFQ33TNFFYZ7YTR25HQH</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Source settings</t>
+          <t>Custom password policy</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KAE27MY7T9RFNXTW210MBD6T</t>
+          <t>h_01KHQP1PV9JMN083DBZQP2BAAM</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/#h_01KAE27MY7T9RFNXTW210MBD6T</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/#h_01KHQP1PV9JMN083DBZQP2BAAM</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Target Settings</t>
+          <t>Termination settings</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01KAE27DSHNQ5FT9VVESXTE5ZG</t>
+          <t>h_01M2J65HX7VB05JNXG9V66F14K</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/#h_01KAE27DSHNQ5FT9VVESXTE5ZG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/#h_01M2J65HX7VB05JNXG9V66F14K</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Unique generation settings</t>
+          <t>Source settings</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1023,41 +1023,41 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01M1NF4VTS85XC2FQEDS0F7182</t>
+          <t>h_01KAE27MY7T9RFNXTW210MBD6T</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/#h_01M1NF4VTS85XC2FQEDS0F7182</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/#h_01KAE27MY7T9RFNXTW210MBD6T</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Unique CN policy</t>
+          <t>Target Settings</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01M1NJMFJFHTZENW9C3258JZ14</t>
+          <t>h_01KAE27DSHNQ5FT9VVESXTE5ZG</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/#h_01M1NJMFJFHTZENW9C3258JZ14</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/#h_01KAE27DSHNQ5FT9VVESXTE5ZG</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Unique UPN policy</t>
+          <t>Target Settings</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1067,19 +1067,19 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01M1NJNZBSZJ98738HKYSZXN4E</t>
+          <t>h_01M2J7ZX5M7N5DP6PWPPRNCT95</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/#h_01M1NJNZBSZJ98738HKYSZXN4E</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/#h_01M2J7ZX5M7N5DP6PWPPRNCT95</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Unique sAMAccountName policy</t>
+          <t>Unique generation settings</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1089,19 +1089,19 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01M1NJS0Q2ZAMXN1BWN3JD0YNR</t>
+          <t>h_01M1NF4VTS85XC2FQEDS0F7182</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/#h_01M1NJS0Q2ZAMXN1BWN3JD0YNR</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/#h_01M1NF4VTS85XC2FQEDS0F7182</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Termination Settings</t>
+          <t>Unique CN policy</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1111,19 +1111,19 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01KDPK17MB1E6W050SNCY9ZE83</t>
+          <t>h_01M1NJMFJFHTZENW9C3258JZ14</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/#h_01KDPK17MB1E6W050SNCY9ZE83</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/#h_01M1NJMFJFHTZENW9C3258JZ14</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Debug Settings</t>
+          <t>Unique UPN policy</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1133,151 +1133,151 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>h_01KADY74D8J9XACJ8XBSMN1TGP</t>
+          <t>h_01M1NJNZBSZJ98738HKYSZXN4E</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/#h_01KADY74D8J9XACJ8XBSMN1TGP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/#h_01M1NJNZBSZJ98738HKYSZXN4E</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Unique sAMAccountName policy</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>h_01KAE1K696HZ0H85MW9JNGJVEY</t>
+          <t>h_01M1NJS0Q2ZAMXN1BWN3JD0YNR</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/#h_01KAE1K696HZ0H85MW9JNGJVEY</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/#h_01M1NJS0Q2ZAMXN1BWN3JD0YNR</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Debug</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>h_01KAE29BFPRBFZCTF419GM72K2</t>
+          <t>h_01KADY74D8J9XACJ8XBSMN1TGP</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/#h_01KAE29BFPRBFZCTF419GM72K2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/#h_01KADY74D8J9XACJ8XBSMN1TGP</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Debug Mode</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01M2JBV5SM1Z3MP0J5Y0MNZRP5</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/#h_01M2JBV5SM1Z3MP0J5Y0MNZRP5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01KAE1K696HZ0H85MW9JNGJVEY</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/#h_01KAE1K696HZ0H85MW9JNGJVEY</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Update the Integration to the Latest Version</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
+          <t>h_01KAE29BFPRBFZCTF419GM72K2</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/#h_01KAE29BFPRBFZCTF419GM72K2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Additional Options</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Insights Dashboard</t>
+          <t>Execute Integration</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1287,76 +1287,142 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>h_01M117SY7RT7X6H656PET0N0M9</t>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/#h_01M117SY7RT7X6H656PET0N0M9</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Viewing Log Dashboard</t>
+          <t>Update the Integration to the Latest Version</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>h_01M117SY83RE6ACR801Z7FDD69</t>
+          <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/#h_01M117SY83RE6ACR801Z7FDD69</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Viewing the Integration Summary Dashboard</t>
+          <t>Additional Options</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>h_01M11D4XQFC2DDR32JGPF15A14</t>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/#h_01M11D4XQFC2DDR32JGPF15A14</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>Insights Dashboard</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>h_01M117SY7RT7X6H656PET0N0M9</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/#h_01M117SY7RT7X6H656PET0N0M9</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Viewing Log Dashboard</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>h_01M117SY83RE6ACR801Z7FDD69</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/#h_01M117SY83RE6ACR801Z7FDD69</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Viewing the Integration Summary Dashboard</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>h_01M11D4XQFC2DDR32JGPF15A14</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/#h_01M11D4XQFC2DDR32JGPF15A14</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t>Viewing the Transaction Dashboard</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>h_01M11D4XQWM422D7GM3XB74FYB</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-to-Dayforce-Multidomain-Integration-Guide/#h_01M11D4XQWM422D7GM3XB74FYB</t>
         </is>
